--- a/data/cramirez.xlsx
+++ b/data/cramirez.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/FIFI/Resumen/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/FIFI/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{27A8781E-A50D-4FD3-83B0-248E5942B5A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95D8537A-AF89-4ED1-8D3E-2EE03E5BED4A}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{27A8781E-A50D-4FD3-83B0-248E5942B5A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A78B0B76-E58E-4EA7-886E-7149EA1D6889}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{7A27F12D-6F9D-4758-B7D5-03B08667753E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="17">
   <si>
     <t>Fecha</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>Carolina Ramirez</t>
+  </si>
+  <si>
+    <t>INV9</t>
   </si>
 </sst>
 </file>
@@ -474,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EEB1E01-21BC-442C-965D-94DEC222FAE4}">
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -1271,7 +1274,7 @@
         <v>15</v>
       </c>
       <c r="D18" s="3">
-        <f>+D17+E17+K17-F17</f>
+        <f t="shared" ref="D18:D27" si="35">+D17+E17+K17-F17</f>
         <v>7239.1690000000008</v>
       </c>
       <c r="G18" s="2">
@@ -1317,7 +1320,7 @@
         <v>15</v>
       </c>
       <c r="D19" s="3">
-        <f>+D18+E18+K18-F18</f>
+        <f t="shared" si="35"/>
         <v>7384.9510000000009</v>
       </c>
       <c r="F19" s="2">
@@ -1327,27 +1330,27 @@
         <v>131.38</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" ref="H19" si="35">+H18+G19</f>
+        <f t="shared" ref="H19" si="36">+H18+G19</f>
         <v>2225.77</v>
       </c>
       <c r="I19" s="4">
-        <f t="shared" ref="I19" si="36">+G19*0.1</f>
+        <f t="shared" ref="I19" si="37">+G19*0.1</f>
         <v>13.138</v>
       </c>
       <c r="J19" s="4">
-        <f t="shared" ref="J19" si="37">+J18+I19</f>
+        <f t="shared" ref="J19" si="38">+J18+I19</f>
         <v>222.57700000000006</v>
       </c>
       <c r="K19" s="4">
-        <f t="shared" ref="K19" si="38">+G19-I19</f>
+        <f t="shared" ref="K19" si="39">+G19-I19</f>
         <v>118.24199999999999</v>
       </c>
       <c r="L19" s="4">
-        <f t="shared" ref="L19" si="39">+L18+K19</f>
+        <f t="shared" ref="L19" si="40">+L18+K19</f>
         <v>2003.1930000000002</v>
       </c>
       <c r="M19" s="4">
-        <f t="shared" ref="M19" si="40">+K19/30</f>
+        <f t="shared" ref="M19" si="41">+K19/30</f>
         <v>3.9413999999999998</v>
       </c>
       <c r="N19" s="5">
@@ -1366,38 +1369,38 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <f>+D19+E19+K19-F19</f>
+        <f t="shared" si="35"/>
         <v>5503.1930000000011</v>
       </c>
       <c r="G20" s="2">
         <v>33.03</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" ref="H20:H21" si="41">+H19+G20</f>
+        <f t="shared" ref="H20:H21" si="42">+H19+G20</f>
         <v>2258.8000000000002</v>
       </c>
       <c r="I20" s="4">
-        <f t="shared" ref="I20:I21" si="42">+G20*0.1</f>
+        <f t="shared" ref="I20:I21" si="43">+G20*0.1</f>
         <v>3.3030000000000004</v>
       </c>
       <c r="J20" s="4">
-        <f t="shared" ref="J20:J21" si="43">+J19+I20</f>
+        <f t="shared" ref="J20:J21" si="44">+J19+I20</f>
         <v>225.88000000000005</v>
       </c>
       <c r="K20" s="4">
-        <f t="shared" ref="K20:K21" si="44">+G20-I20</f>
+        <f t="shared" ref="K20:K21" si="45">+G20-I20</f>
         <v>29.727</v>
       </c>
       <c r="L20" s="4">
-        <f t="shared" ref="L20:L21" si="45">+L19+K20</f>
+        <f t="shared" ref="L20:L21" si="46">+L19+K20</f>
         <v>2032.9200000000003</v>
       </c>
       <c r="M20" s="4">
-        <f t="shared" ref="M20:M21" si="46">+K20/30</f>
+        <f t="shared" ref="M20:M21" si="47">+K20/30</f>
         <v>0.9909</v>
       </c>
       <c r="N20" s="5">
-        <f t="shared" ref="N20:N21" si="47">+G20/D20</f>
+        <f t="shared" ref="N20:N21" si="48">+G20/D20</f>
         <v>6.0019701289778489E-3</v>
       </c>
     </row>
@@ -1412,7 +1415,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <f>+D20+E20+K20-F20</f>
+        <f t="shared" si="35"/>
         <v>5532.920000000001</v>
       </c>
       <c r="E21" s="7"/>
@@ -1420,31 +1423,31 @@
         <v>214.17</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>2472.9700000000003</v>
       </c>
       <c r="I21" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>21.417000000000002</v>
       </c>
       <c r="J21" s="4">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>247.29700000000005</v>
       </c>
       <c r="K21" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>192.75299999999999</v>
       </c>
       <c r="L21" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>2225.6730000000002</v>
       </c>
       <c r="M21" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>6.4250999999999996</v>
       </c>
       <c r="N21" s="5">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>3.8708313151102847E-2</v>
       </c>
     </row>
@@ -1459,38 +1462,38 @@
         <v>15</v>
       </c>
       <c r="D22" s="3">
-        <f>+D21+E21+K21-F21</f>
+        <f t="shared" si="35"/>
         <v>5725.6730000000007</v>
       </c>
       <c r="G22" s="2">
         <v>180.99</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" ref="H22" si="48">+H21+G22</f>
+        <f t="shared" ref="H22" si="49">+H21+G22</f>
         <v>2653.96</v>
       </c>
       <c r="I22" s="4">
-        <f t="shared" ref="I22" si="49">+G22*0.1</f>
+        <f t="shared" ref="I22" si="50">+G22*0.1</f>
         <v>18.099</v>
       </c>
       <c r="J22" s="4">
-        <f t="shared" ref="J22" si="50">+J21+I22</f>
+        <f t="shared" ref="J22" si="51">+J21+I22</f>
         <v>265.39600000000007</v>
       </c>
       <c r="K22" s="4">
-        <f t="shared" ref="K22" si="51">+G22-I22</f>
+        <f t="shared" ref="K22" si="52">+G22-I22</f>
         <v>162.89100000000002</v>
       </c>
       <c r="L22" s="4">
-        <f t="shared" ref="L22" si="52">+L21+K22</f>
+        <f t="shared" ref="L22" si="53">+L21+K22</f>
         <v>2388.5640000000003</v>
       </c>
       <c r="M22" s="4">
-        <f t="shared" ref="M22" si="53">+K22/30</f>
+        <f t="shared" ref="M22" si="54">+K22/30</f>
         <v>5.4297000000000004</v>
       </c>
       <c r="N22" s="5">
-        <f t="shared" ref="N22" si="54">+G22/D22</f>
+        <f t="shared" ref="N22" si="55">+G22/D22</f>
         <v>3.1610257868376346E-2</v>
       </c>
     </row>
@@ -1505,38 +1508,38 @@
         <v>15</v>
       </c>
       <c r="D23" s="3">
-        <f>+D22+E22+K22-F22</f>
+        <f t="shared" si="35"/>
         <v>5888.5640000000003</v>
       </c>
       <c r="G23" s="2">
         <v>175.41</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" ref="H23:H24" si="55">+H22+G23</f>
+        <f t="shared" ref="H23:H24" si="56">+H22+G23</f>
         <v>2829.37</v>
       </c>
       <c r="I23" s="4">
-        <f t="shared" ref="I23:I24" si="56">+G23*0.1</f>
+        <f t="shared" ref="I23:I24" si="57">+G23*0.1</f>
         <v>17.541</v>
       </c>
       <c r="J23" s="4">
-        <f t="shared" ref="J23:J24" si="57">+J22+I23</f>
+        <f t="shared" ref="J23:J24" si="58">+J22+I23</f>
         <v>282.93700000000007</v>
       </c>
       <c r="K23" s="4">
-        <f t="shared" ref="K23:K24" si="58">+G23-I23</f>
+        <f t="shared" ref="K23:K24" si="59">+G23-I23</f>
         <v>157.869</v>
       </c>
       <c r="L23" s="4">
-        <f t="shared" ref="L23:L24" si="59">+L22+K23</f>
+        <f t="shared" ref="L23:L24" si="60">+L22+K23</f>
         <v>2546.4330000000004</v>
       </c>
       <c r="M23" s="4">
-        <f t="shared" ref="M23:M24" si="60">+K23/30</f>
+        <f t="shared" ref="M23:M24" si="61">+K23/30</f>
         <v>5.2622999999999998</v>
       </c>
       <c r="N23" s="5">
-        <f t="shared" ref="N23:N24" si="61">+G23/D23</f>
+        <f t="shared" ref="N23:N24" si="62">+G23/D23</f>
         <v>2.9788247185561709E-2</v>
       </c>
     </row>
@@ -1551,35 +1554,219 @@
         <v>15</v>
       </c>
       <c r="D24" s="3">
-        <f>+D23+E23+K23-F23</f>
+        <f t="shared" si="35"/>
         <v>6046.433</v>
       </c>
+      <c r="G24" s="2">
+        <v>84.65</v>
+      </c>
       <c r="H24" s="4">
-        <f t="shared" si="55"/>
-        <v>2829.37</v>
+        <f t="shared" si="56"/>
+        <v>2914.02</v>
       </c>
       <c r="I24" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
+        <v>8.4650000000000016</v>
+      </c>
+      <c r="J24" s="4">
+        <f t="shared" si="58"/>
+        <v>291.40200000000004</v>
+      </c>
+      <c r="K24" s="4">
+        <f t="shared" si="59"/>
+        <v>76.185000000000002</v>
+      </c>
+      <c r="L24" s="4">
+        <f t="shared" si="60"/>
+        <v>2622.6180000000004</v>
+      </c>
+      <c r="M24" s="4">
+        <f t="shared" si="61"/>
+        <v>2.5394999999999999</v>
+      </c>
+      <c r="N24" s="5">
+        <f t="shared" si="62"/>
+        <v>1.3999989746020507E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>45902</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="3">
+        <f t="shared" si="35"/>
+        <v>6122.6180000000004</v>
+      </c>
+      <c r="G25" s="2">
+        <v>140.82</v>
+      </c>
+      <c r="H25" s="4">
+        <f t="shared" ref="H25:H27" si="63">+H24+G25</f>
+        <v>3054.84</v>
+      </c>
+      <c r="I25" s="4">
+        <f t="shared" ref="I25:I27" si="64">+G25*0.1</f>
+        <v>14.082000000000001</v>
+      </c>
+      <c r="J25" s="4">
+        <f t="shared" ref="J25:J27" si="65">+J24+I25</f>
+        <v>305.48400000000004</v>
+      </c>
+      <c r="K25" s="4">
+        <f t="shared" ref="K25:K27" si="66">+G25-I25</f>
+        <v>126.738</v>
+      </c>
+      <c r="L25" s="4">
+        <f t="shared" ref="L25:L27" si="67">+L24+K25</f>
+        <v>2749.3560000000002</v>
+      </c>
+      <c r="M25" s="4">
+        <f t="shared" ref="M25:M27" si="68">+K25/30</f>
+        <v>4.2245999999999997</v>
+      </c>
+      <c r="N25" s="5">
+        <f t="shared" ref="N25:N27" si="69">+G25/D25</f>
+        <v>2.2999965047631583E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>45932</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="3">
+        <f t="shared" si="35"/>
+        <v>6249.3560000000007</v>
+      </c>
+      <c r="G26" s="2">
+        <v>131.24</v>
+      </c>
+      <c r="H26" s="4">
+        <f t="shared" si="63"/>
+        <v>3186.08</v>
+      </c>
+      <c r="I26" s="4">
+        <f t="shared" si="64"/>
+        <v>13.124000000000002</v>
+      </c>
+      <c r="J26" s="4">
+        <f t="shared" si="65"/>
+        <v>318.60800000000006</v>
+      </c>
+      <c r="K26" s="4">
+        <f t="shared" si="66"/>
+        <v>118.11600000000001</v>
+      </c>
+      <c r="L26" s="4">
+        <f t="shared" si="67"/>
+        <v>2867.4720000000002</v>
+      </c>
+      <c r="M26" s="4">
+        <f t="shared" si="68"/>
+        <v>3.9372000000000003</v>
+      </c>
+      <c r="N26" s="5">
+        <f t="shared" si="69"/>
+        <v>2.100056389810406E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>45963</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="3">
+        <f t="shared" si="35"/>
+        <v>6367.4720000000007</v>
+      </c>
+      <c r="G27" s="2">
+        <v>229.23</v>
+      </c>
+      <c r="H27" s="4">
+        <f t="shared" si="63"/>
+        <v>3415.31</v>
+      </c>
+      <c r="I27" s="4">
+        <f t="shared" si="64"/>
+        <v>22.923000000000002</v>
+      </c>
+      <c r="J27" s="4">
+        <f t="shared" si="65"/>
+        <v>341.53100000000006</v>
+      </c>
+      <c r="K27" s="4">
+        <f t="shared" si="66"/>
+        <v>206.30699999999999</v>
+      </c>
+      <c r="L27" s="4">
+        <f t="shared" si="67"/>
+        <v>3073.779</v>
+      </c>
+      <c r="M27" s="4">
+        <f t="shared" si="68"/>
+        <v>6.8769</v>
+      </c>
+      <c r="N27" s="5">
+        <f t="shared" si="69"/>
+        <v>3.6000158304583037E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>45993</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="3">
+        <f t="shared" ref="D28" si="70">+D27+E27+K27-F27</f>
+        <v>6573.7790000000005</v>
+      </c>
+      <c r="H28" s="4">
+        <f t="shared" ref="H28" si="71">+H27+G28</f>
+        <v>3415.31</v>
+      </c>
+      <c r="I28" s="4">
+        <f t="shared" ref="I28" si="72">+G28*0.1</f>
         <v>0</v>
       </c>
-      <c r="J24" s="4">
-        <f t="shared" si="57"/>
-        <v>282.93700000000007</v>
-      </c>
-      <c r="K24" s="4">
-        <f t="shared" si="58"/>
+      <c r="J28" s="4">
+        <f t="shared" ref="J28" si="73">+J27+I28</f>
+        <v>341.53100000000006</v>
+      </c>
+      <c r="K28" s="4">
+        <f t="shared" ref="K28" si="74">+G28-I28</f>
         <v>0</v>
       </c>
-      <c r="L24" s="4">
-        <f t="shared" si="59"/>
-        <v>2546.4330000000004</v>
-      </c>
-      <c r="M24" s="4">
-        <f t="shared" si="60"/>
+      <c r="L28" s="4">
+        <f t="shared" ref="L28" si="75">+L27+K28</f>
+        <v>3073.779</v>
+      </c>
+      <c r="M28" s="4">
+        <f t="shared" ref="M28" si="76">+K28/30</f>
         <v>0</v>
       </c>
-      <c r="N24" s="5">
-        <f t="shared" si="61"/>
+      <c r="N28" s="5">
+        <f t="shared" ref="N28" si="77">+G28/D28</f>
         <v>0</v>
       </c>
     </row>

--- a/data/cramirez.xlsx
+++ b/data/cramirez.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\OneDrive\Documentos\Proyectos\FIFI\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/Proyectos/FIFI/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68EFCD14-B825-44BE-A779-2038E4BD8F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{68EFCD14-B825-44BE-A779-2038E4BD8F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16179844-285C-4F21-B0C7-3169C076D108}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{7A27F12D-6F9D-4758-B7D5-03B08667753E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="16">
   <si>
     <t>Fecha</t>
   </si>
@@ -474,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EEB1E01-21BC-442C-965D-94DEC222FAE4}">
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -1877,33 +1877,174 @@
         <f t="shared" si="78"/>
         <v>6906.9319999999998</v>
       </c>
+      <c r="G31" s="2">
+        <v>88.99</v>
+      </c>
       <c r="H31" s="4">
         <f t="shared" si="79"/>
-        <v>3785.4800000000005</v>
+        <v>3874.4700000000003</v>
       </c>
       <c r="I31" s="4">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>8.8989999999999991</v>
       </c>
       <c r="J31" s="4">
         <f t="shared" si="81"/>
-        <v>378.54800000000006</v>
+        <v>387.44700000000006</v>
       </c>
       <c r="K31" s="4">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>80.090999999999994</v>
       </c>
       <c r="L31" s="4">
         <f t="shared" si="83"/>
-        <v>3406.9320000000002</v>
+        <v>3487.0230000000001</v>
       </c>
       <c r="M31" s="4">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>2.6696999999999997</v>
       </c>
       <c r="N31" s="5">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>1.2884157539121567E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="3">
+        <f t="shared" ref="D32:D34" si="86">+D31+E31+K31-F31</f>
+        <v>6987.0230000000001</v>
+      </c>
+      <c r="G32" s="2">
+        <v>46.87</v>
+      </c>
+      <c r="H32" s="4">
+        <f t="shared" ref="H32:H34" si="87">+H31+G32</f>
+        <v>3921.34</v>
+      </c>
+      <c r="I32" s="4">
+        <f t="shared" ref="I32:I34" si="88">+G32*0.1</f>
+        <v>4.6870000000000003</v>
+      </c>
+      <c r="J32" s="4">
+        <f t="shared" ref="J32:J34" si="89">+J31+I32</f>
+        <v>392.13400000000007</v>
+      </c>
+      <c r="K32" s="4">
+        <f t="shared" ref="K32:K34" si="90">+G32-I32</f>
+        <v>42.183</v>
+      </c>
+      <c r="L32" s="4">
+        <f t="shared" ref="L32:L34" si="91">+L31+K32</f>
+        <v>3529.2060000000001</v>
+      </c>
+      <c r="M32" s="4">
+        <f t="shared" ref="M32:M34" si="92">+K32/30</f>
+        <v>1.4060999999999999</v>
+      </c>
+      <c r="N32" s="5">
+        <f t="shared" ref="N32:N34" si="93">+G32/D32</f>
+        <v>6.7081502379482648E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>46144</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="3">
+        <f t="shared" si="86"/>
+        <v>7029.2060000000001</v>
+      </c>
+      <c r="G33" s="2">
+        <v>167</v>
+      </c>
+      <c r="H33" s="4">
+        <f t="shared" si="87"/>
+        <v>4088.34</v>
+      </c>
+      <c r="I33" s="4">
+        <f t="shared" si="88"/>
+        <v>16.7</v>
+      </c>
+      <c r="J33" s="4">
+        <f t="shared" si="89"/>
+        <v>408.83400000000006</v>
+      </c>
+      <c r="K33" s="4">
+        <f t="shared" si="90"/>
+        <v>150.30000000000001</v>
+      </c>
+      <c r="L33" s="4">
+        <f t="shared" si="91"/>
+        <v>3679.5060000000003</v>
+      </c>
+      <c r="M33" s="4">
+        <f t="shared" si="92"/>
+        <v>5.0100000000000007</v>
+      </c>
+      <c r="N33" s="5">
+        <f t="shared" si="93"/>
+        <v>2.3758017619628733E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="3">
+        <f t="shared" si="86"/>
+        <v>7179.5060000000003</v>
+      </c>
+      <c r="G34" s="2">
+        <v>130.88</v>
+      </c>
+      <c r="H34" s="4">
+        <f t="shared" si="87"/>
+        <v>4219.22</v>
+      </c>
+      <c r="I34" s="4">
+        <f t="shared" si="88"/>
+        <v>13.088000000000001</v>
+      </c>
+      <c r="J34" s="4">
+        <f t="shared" si="89"/>
+        <v>421.92200000000008</v>
+      </c>
+      <c r="K34" s="4">
+        <f t="shared" si="90"/>
+        <v>117.792</v>
+      </c>
+      <c r="L34" s="4">
+        <f t="shared" si="91"/>
+        <v>3797.2980000000002</v>
+      </c>
+      <c r="M34" s="4">
+        <f t="shared" si="92"/>
+        <v>3.9264000000000001</v>
+      </c>
+      <c r="N34" s="5">
+        <f t="shared" si="93"/>
+        <v>1.822966649794568E-2</v>
       </c>
     </row>
   </sheetData>
